--- a/Hoadon/HD2026/HDVao/9/3502550210_HDDienTuKhongMa.xlsx
+++ b/Hoadon/HD2026/HDVao/9/3502550210_HDDienTuKhongMa.xlsx
@@ -1238,6 +1238,164 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>1664884</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3500101386</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J19" s="6"/>
+      <c r="K19" s="13" t="n">
+        <v>139560.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>8135.0</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>147695.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>1664888</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3500101386</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J20" s="6"/>
+      <c r="K20" s="13" t="n">
+        <v>588080.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>34320.0</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>622400.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>
